--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.5.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.5.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.5.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.5.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="51" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œIn</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SATURDAY, July 7.â€”The market this morn-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L29: isolated marker/symbol line :: 8</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: music. Much credit is due to Miss Coon long as they can. They are looking out | of the city, was attacked last night | LIVERPOOL, July 11, 11.30 a.m.â€”Spring wheat,</t>
+          <t>L485: abbreviation/spacing may be garbled :: music. Much credit is due to Miss Coon long as they can. They are looking out | of the city, was attacked last night | LIVERPOOL, July 11, 11.30 a.m.—Spring wheat,</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>683</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -712,12 +716,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MONTREAL, July 11, 1 p. m.- m.â€”Flourâ€”Receipts,</t>
+          <t>L730: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): DG6 (letter/digit mix) :: DG6 ， 101</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and we will support it.â€� And some of fun. He commenced his game by visiting grants have received this spring in Toronto The News says : A drive through the</t>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: occupied prominent positions, amongst the meantime Kate started up a howl worse whose duty it wase€1-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -805,26 +809,22 @@
           <t>L37: suspicious token(s): 10c (letter/digit mix), 124c (letter/digit mix) :: Strawberries were scarce at 10c to 124c a basket,</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: energies to clearing their land and raising noon to hunt her lord and master. After which a Rev. Mr. Mackay is Secretary, trouble of cutting and curing. Nowhereis I SA...</t>
+          <t>L163: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — • ---</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L232: isolated marker/symbol line :: )</t>
+          <t>L163: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — • ---</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Flamboroâ€™ line (many of its pupils having | on the g... â€”,â€”_</t>
+          <t>L90: punctuation artifact: repeated periods :: Flamboro’ line (many of its pupils having | on the g... —,—_</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -866,12 +866,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -900,14 +900,10 @@
           <t>L38: suspicious token(s): 7c (letter/digit mix), 10c (letter/digit mix) :: and cherries brought 7c to 10c a basket. There</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: downcast.â€”Buffalo News.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: of the duties they owed to tâ€˜eir children | manner a policeman appeared on the scene | pists for the sad plight in which they found | are badly burned up, and the su...</t>
+          <t>L314: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: Burton, the other for Donaldson, the I called on the minister and apologised for I ---•----</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -919,7 +915,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L664: symbol-only separator/garbage line :: 1816.</t>
+          <t>L232: isolated marker/symbol line :: )</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -935,7 +931,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L578: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------â€¢ | of course, they were turned out by the</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • In 1834 the people began to feel the</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -991,14 +987,10 @@
           <t>L40: suspicious token(s): 25c (letter/digit mix), 30c (letter/digit mix), 20c (letter/digit mix) :: ket selling at 25c and 30c each. Eggs sold at 20c</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L647: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): OTTawa (odd internal casing) :: OTTawa, July 11.â€” A young man named</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Steelâ€™s blacksmith shop now stands. We | officer in the choicest language when he was | valued; benumbed with cold and well ing an!</t>
+          <t>L375: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Grummets, the Barlows, the Willards, the |the liquor store.•</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -1008,7 +1000,11 @@
           <t>L1077: symbol-only separator/garbage line :: $15.</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L664: symbol-only separator/garbage line :: 1816.</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
@@ -1016,16 +1012,12 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------â€¢ -------;â€” | for September, 862c for December. Cornâ€”494c</t>
-        </is>
-      </c>
+      <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr">
         <is>
-          <t>L1089: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Chicago, July 11, 1.00 p.m.-Close-Wheatâ€”â€”</t>
+          <t>L1089: abbreviation/spacing may be garbled :: Chicago, July 11, 1.00 p.m.-Close-Wheat——</t>
         </is>
       </c>
       <c r="W6" s="1" t="inlineStr">
@@ -1074,14 +1066,10 @@
           <t>L41: suspicious token(s): 22c (letter/digit mix), 1b (letter/digit mix) :: a dozen and butter at 22c a 1b. Lamb sold at</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L753: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: firmly held; maize, nil. Cargoes on passage â€”</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Flamboroâ€™ line (many of its pupils having | on the g... â€”,â€”_</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • In 1834 the people began to feel the</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1095,15 +1083,11 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€” â€¢ ---</t>
+          <t>L163: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — • ---</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr">
-        <is>
-          <t>L739: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------â€¢------------I 11,000. Market fairly active.</t>
-        </is>
-      </c>
+      <c r="S7" s="1" t="inlineStr"/>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1149,14 +1133,10 @@
           <t>L42: suspicious token(s): 60c (letter/digit mix), 80c (letter/digit mix), 75c (letter/digit mix) :: 60c to 80c for forequarters and 75c to $1 for hind,</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing one that he especially regretted losingâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: occupied prominent positions, amongst the meantime Kate started up a howl worse whose duty it waseâ‚¬1-</t>
+          <t>L496: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: desperate struggle with the men and finally 1 fair. —•—</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1212,14 +1192,10 @@
           <t>L43: suspicious token(s): 10c (letter/digit mix), 11c (letter/digit mix), 1b (letter/digit mix) :: or 10c to 11c a 1b. by the carcase; mutton</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L941: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Mr. H. H. Dewart, President of the</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from whom much of my informa- | five minutes about two hundred people | citizens and for the active charity of the | â€”_</t>
+          <t>L578: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -------------------• | of course, they were turned out by the</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1229,7 +1205,7 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: ,â€” ----------, --. â€” I â€” Eâ€” - IM 1 for strong bakers. Grain-Wheat-Market</t>
+          <t>L221: punctuation artifact: double/multiple hyphen :: ,— ----------, --. — I — E— - IM 1 for strong bakers. Grain-Wheat-Market</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1249,12 +1225,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1271,14 +1247,10 @@
           <t>L44: suspicious token(s): 8c (letter/digit mix), 9c (letter/digit mix), 4c (letter/digit mix), 5c (letter/digit mix) :: brought 8c to 9c by the carcase ; veal, 4c to 5c a</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L1003: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Mr. James Forbes, of Oneida Town-</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 98c (letter/digit mix) :: settlers as part Of his salary. In the same sent thoughthit was best to give Kate a bath classes read, exposing the fraud by which ers of Ashbury Methodist Episcopal C...</t>
+          <t>L587: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: - ----------• -----------Sales, 424,000 bushels No. 2 red for August</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1288,7 +1260,7 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: mill, where for many years they kept a -a -------------4â€”3 -------------# +k. + â€”shinâ€™s</t>
+          <t>L302: punctuation artifact: double/multiple hyphen :: mill, where for many years they kept a -a -------------4—3 -------------# +k. + —shin’s</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1313,7 +1285,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1330,14 +1302,10 @@
           <t>L45: suspicious token(s): 4c (letter/digit mix), 6c (letter/digit mix), 1b (letter/digit mix) :: lb., and beef 4c to 6c per 1b. by the quarter.</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L1050: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: in a few days.â€”Toronto Globe.</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 514c (letter/digit mix) :: their arms and started through the bush to A LIQUOR CASE. vain is the net laid insight of any bird. not become public until today, and Joseph 514c ontract - â€”+â€”</t>
+          <t>L607: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------• -------;— | for September, 862c for December. Corn—494c</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1347,7 +1315,7 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: Burton, the other for Donaldson, the I called on the minister and apologised for I ---â€¢----</t>
+          <t>L314: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: Burton, the other for Donaldson, the I called on the minister and apologised for I ---•----</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1372,7 +1340,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1389,14 +1357,10 @@
           <t>L99: suspicious token(s): IEat (odd internal casing), 15c (letter/digit mix) :: in the Sheffield school was one Elias Smith, |keeping up her music. Jim was safely |are sending letters home, which are being IEat 15c._</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L1089: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Chicago, July 11, 1.00 p.m.-Close-Wheatâ€”â€”</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: was buried there was old Mr. Weaver, | Daniel Henry Fined $30 for a Breach of | Lloydâ€™s Weekly Newspaper of June 7th. The | committed the assault, has not yet been T...</t>
+          <t>L627: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -— ----------------•-------------nominally for August, $7 574 for September.</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1431,7 +1395,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1445,17 +1409,13 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 98c (letter/digit mix) :: settlers as part Of his salary. In the same sent thoughthit was best to give Kate a bath classes read, exposing the fraud by which ers of Ashbury Methodist Episcopal C...</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L1107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): OHiOAGO (odd internal casing), JULy (odd internal casing) :: UNION Brock YABDS.â€” OHiOAGO, JULy 11., 7.30</t>
-        </is>
-      </c>
+          <t>L102: suspicious token(s): 98c (letter/digit mix) :: settlers as part Of his salary. In the same sent thoughthit was best to give Kate a bath classes read, exposing the fraud by which ers of Ashbury Methodist Episcopal C...</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 6c (letter/digit mix) :: proved in the end to be the last resting- charged by License Inspector J. I. Mac- â€”something like a cow-shed-with a plat- |up to him and asked if he were not Mr. qua...</t>
+          <t>L739: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -------------------•------------I 11,000. Market fairly active.</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1490,7 +1450,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1508,11 +1468,7 @@
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): peRtr (odd internal casing) :: a a by a nt of a eter was mens for to one aroras of wankey BP and they are eted once in the Enening tague who let ate Date By as the peRtrâ€™s e ad a : B : 1 1 1 5</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
@@ -1563,11 +1519,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€” â€¢ ---</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr"/>
@@ -1618,11 +1570,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: these veteransâ€”these noble men and women</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
@@ -1673,11 +1621,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: against the forestâ€”a place on one of the</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
@@ -1685,7 +1629,7 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L377: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Eagles, John Wells and his brother James. | defendant guilty and fined him $30 and | to go ---- â€” . 3</t>
+          <t>L377: punctuation artifact: double/multiple hyphen :: Eagles, John Wells and his brother James. | defendant guilty and fined him $30 and | to go ---- — . 3</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1716,11 +1660,7 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MONTREAL, July 11, 1 p. m.â€”Flourâ€”Receipts,</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
@@ -1728,7 +1668,7 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: the older members of them are all dead, -------------------------- I Â« Well, I donâ€™t know what they are sending</t>
+          <t>L380: punctuation artifact: double/multiple hyphen :: the older members of them are all dead, -------------------------- I « Well, I don’t know what they are sending</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
@@ -1755,15 +1695,11 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 514c (letter/digit mix) :: their arms and started through the bush to A LIQUOR CASE. vain is the net laid insight of any bird. not become public until today, and Joseph 514c ontract - â€”+â€”</t>
+          <t>L115: suspicious token(s): 514c (letter/digit mix) :: their arms and started through the bush to A LIQUOR CASE. vain is the net laid insight of any bird. not become public until today, and Joseph 514c ontract - —+—</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: ,â€” ----------, --. â€” I â€” Eâ€” - IM 1 for strong bakers. Grain-Wheat-Market</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
@@ -1802,11 +1738,7 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: $3 25. Provisionsâ€”Pork, $18 00 to $19 00. Lard,</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr"/>
@@ -1841,15 +1773,11 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 6c (letter/digit mix) :: proved in the end to be the last resting- charged by License Inspector J. I. Mac- â€”something like a cow-shed-with a plat- |up to him and asked if he were not Mr. qua...</t>
+          <t>L124: suspicious token(s): 6c (letter/digit mix) :: proved in the end to be the last resting- charged by License Inspector J. I. Mac- —something like a cow-shed-with a plat- |up to him and asked if he were not Mr. quart...</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 17c (letter/digit mix), 19c (letter/digit mix), 15c (letter/digit mix), 17c (letter/digit mix) :: burg, 17c to 19c; western, 15c to 17c. Eggsâ€”Firm,</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
@@ -1857,7 +1785,7 @@
       <c r="P21" s="1" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; double/multiple hyphen :: *...................................1 .7 _!== ---------â€”â€” 1.46â€” 'right side of the body. He made a | holders offer moderately. Corn steady; demand</t>
+          <t>L494: punctuation artifact: repeated periods; double/multiple hyphen :: *...................................1 .7 _!== ---------—— 1.46— 'right side of the body. He made a | holders offer moderately. Corn steady; demand</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -1888,11 +1816,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: mill, where for many years they kept a -a -------------4â€”3 -------------# +k. + â€”shinâ€™s</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
@@ -1900,7 +1824,7 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L546: punctuation artifact: double/multiple hyphen :: A second regular Baptist Church was --</t>
+          <t>L496: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: desperate struggle with the men and finally 1 fair. —•—</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1931,11 +1855,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L309: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: .___________adonâ€™t mind it myself ; but it is sickening to the Dominie yelled for the police. Some The Dairy Markets.</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
@@ -1943,7 +1863,7 @@
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L554: punctuation artifact: repeated commas :: Miss Pearson,, daughter of the Rev. F. D. of Co But Methodist Church The</t>
+          <t>L546: punctuation artifact: double/multiple hyphen :: A second regular Baptist Church was --</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -1974,11 +1894,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L311: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: that she sent see the poor women and children cryingfor men in a neighboring barber shop inter- | INGERSOLL, July 10.â€”This week 35 factories</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
@@ -1986,7 +1902,7 @@
       <c r="P24" s="1" t="inlineStr"/>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: Boysâ€™ Own Mission Band of Erskine Church, ---------- ____________-</t>
+          <t>L554: punctuation artifact: repeated commas :: Miss Pearson,, daughter of the Rev. F. D. of Co But Methodist Church The</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
@@ -2013,15 +1929,11 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): peRtr (odd internal casing) :: a a by a nt of a eter was mens for to one aroras of wankey BP and they are eted once in the Enening tague who let ate Date By as the peRtrâ€™s e ad a : B : 1 1 1 5</t>
+          <t>L132: suspicious token(s): peRtr’s (odd internal casing) :: a a by a nt of a eter was mens for to one aroras of wankey BP and they are eted once in the Enening tague who let ate Date By as the peRtr’s e ad a : B : 1 1 1 5</t>
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: Burton, the other for Donaldson, the I called on the minister and apologised for I ---â€¢----</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
@@ -2029,7 +1941,7 @@
       <c r="P25" s="1" t="inlineStr"/>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>L578: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------â€¢ | of course, they were turned out by the</t>
+          <t>L571: punctuation artifact: double/multiple hyphen :: Boys’ Own Mission Band of Erskine Church, ---------- ____________-</t>
         </is>
       </c>
       <c r="R25" s="1" t="inlineStr"/>
@@ -2060,11 +1972,7 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: covered. A few Canucks who came to this I and eight remain. At to-dayâ€™s market wheats</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
@@ -2072,7 +1980,7 @@
       <c r="P26" s="1" t="inlineStr"/>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: - ----------â€¢ -----------Sales, 424,000 bushels No. 2 red for August</t>
+          <t>L578: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -------------------• | of course, they were turned out by the</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2103,11 +2011,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: city one day last week are believed to have I were weaker. Last weekâ€™s advance was barely</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr"/>
@@ -2115,7 +2019,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L588: punctuation artifact: double/multiple hyphen | suspicious token(s): 16c (letter/digit mix), 887c (letter/digit mix) :: Grimsby Camp Guessing.---at 88 5-16c to 887c; 496,000 bushels for Septem-</t>
+          <t>L587: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: - ----------• -----------Sales, 424,000 bushels No. 2 red for August</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2146,11 +2050,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: able articles of jewellery were tied inadearer._â€”</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr"/>
@@ -2158,7 +2058,7 @@
       <c r="P28" s="1" t="inlineStr"/>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>L602: punctuation artifact: repeated periods :: LOL ..11 Toledo Markets.</t>
+          <t>L588: punctuation artifact: double/multiple hyphen | suspicious token(s): 16c (letter/digit mix), 887c (letter/digit mix) :: Grimsby Camp Guessing.---at 88 5-16c to 887c; 496,000 bushels for Septem-</t>
         </is>
       </c>
       <c r="R28" s="1" t="inlineStr"/>
@@ -2189,11 +2089,7 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: custom collector found nothing, of course, |(Beerbohmâ€™s Telegram.)</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr"/>
@@ -2201,7 +2097,7 @@
       <c r="P29" s="1" t="inlineStr"/>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------â€¢ -------;â€” | for September, 862c for December. Cornâ€”494c</t>
+          <t>L602: punctuation artifact: repeated periods :: LOL ..11 Toledo Markets.</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2223,7 +2119,7 @@
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>L647: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): OTTawa (odd internal casing) :: OTTawa, July 11.â€” A young man named</t>
+          <t>L647: suspicious token(s): OTTawa (odd internal casing) :: OTTawa, July 11.— A young man named</t>
         </is>
       </c>
       <c r="I30" s="1" t="inlineStr">
@@ -2232,11 +2128,7 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L361: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of pies and cakes | tea and cake. We had as much as ever downcast.â€”Buffalo News.</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr"/>
@@ -2244,7 +2136,7 @@
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: -â€” ----------------â€¢-------------nominally for August, $7 574 for September.</t>
+          <t>L607: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------• -------;— | for September, 862c for December. Corn—494c</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2275,11 +2167,7 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Grummets, the Barlows, the Willards, the |the liquor store.â€¢</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr"/>
@@ -2287,7 +2175,7 @@
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L699: punctuation artifact: double/multiple hyphen :: keeper. Young women applied to him for | ---------_</t>
+          <t>L627: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -— ----------------•-------------nominally for August, $7 574 for September.</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2318,11 +2206,7 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L377: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Eagles, John Wells and his brother James. | defendant guilty and fined him $30 and | to go ---- â€” . 3</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
@@ -2330,7 +2214,7 @@
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L711: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: besides, he, owned a big farm in the in- ------- ----â€” ------------</t>
+          <t>L699: punctuation artifact: double/multiple hyphen :: keeper. Young women applied to him for | ---------_</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2361,11 +2245,7 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: the older members of them are all dead, -------------------------- I Â« Well, I donâ€™t know what they are sending</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
@@ -2373,7 +2253,7 @@
       <c r="P33" s="1" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L735: punctuation artifact: repeated periods :: plump and fill.. The fall wheat is now Ishipments, 6,431; left over, about 4,000. Light</t>
+          <t>L711: punctuation artifact: double/multiple hyphen :: besides, he, owned a big farm in the in- ------- ----— ------------</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2400,15 +2280,11 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 17c (letter/digit mix), 19c (letter/digit mix), 15c (letter/digit mix), 17c (letter/digit mix) :: burg, 17c to 19c; western, 15c to 17c. Eggsâ€”Firm,</t>
+          <t>L230: suspicious token(s): 17c (letter/digit mix), 19c (letter/digit mix), 15c (letter/digit mix), 17c (letter/digit mix) :: burg, 17c to 19c; western, 15c to 17c. Eggs—Firm,</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”1 1 them out for; we have got hundreds upon</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
@@ -2416,7 +2292,7 @@
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>L739: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------â€¢------------I 11,000. Market fairly active.</t>
+          <t>L735: punctuation artifact: repeated periods :: plump and fill.. The fall wheat is now Ishipments, 6,431; left over, about 4,000. Light</t>
         </is>
       </c>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2443,21 +2319,21 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>L313: suspicious token(s): twolottEs (odd internal casing) :: Mackay gave no twolottEs OUS for ET ^MÂ°h^*^:^</t>
+          <t>L313: suspicious token(s): twolottEs (odd internal casing) :: Mackay gave no twolottEs OUS for ET ^M°h^*^:^</t>
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L413: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ In 1834 the people began to feel the</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
       <c r="O35" s="1" t="inlineStr"/>
       <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t>L739: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: -------------------•------------I 11,000. Market fairly active.</t>
+        </is>
+      </c>
       <c r="R35" s="1" t="inlineStr"/>
       <c r="S35" s="1" t="inlineStr"/>
       <c r="T35" s="1" t="inlineStr"/>
@@ -2486,11 +2362,7 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: store on the place where Bondâ€™s store now</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
@@ -2525,11 +2397,7 @@
         </is>
       </c>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, July 11.â€”Floating cargoes-Wheat</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr"/>
@@ -2564,11 +2432,7 @@
         </is>
       </c>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L447: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: firmly held; maize, nil. Cargoes on passageâ€”</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr"/>
@@ -2603,11 +2467,7 @@
         </is>
       </c>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Minnesota flour 22s 3d, was 22s. Londonâ€”Good</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr"/>
@@ -2642,11 +2502,7 @@
         </is>
       </c>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PARIS, July 11.â€”Wheat and flour, firm.</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr"/>
@@ -2681,11 +2537,7 @@
         </is>
       </c>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L460: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LIVERPOOL, July 11.â€”Spot-Wheat, firmly</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr"/>
@@ -2720,11 +2572,7 @@
         </is>
       </c>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L461: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: held; maize, dull. Maize, 4s 103dâ€”halfpenny</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr"/>
@@ -2759,11 +2607,7 @@
         </is>
       </c>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L462: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: cheaper. Peas, 6s 1dâ€”1d dearer. On passage to</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr"/>
@@ -2794,15 +2638,11 @@
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>L591: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 974c (letter/digit mix), 97c (letter/digit mix) :: Grimsby Camp Ground Company, offered at 974c to 97c. Ryeâ€”Nominal. Corn-Market</t>
+          <t>L591: suspicious token(s): 974c (letter/digit mix), 97c (letter/digit mix) :: Grimsby Camp Ground Company, offered at 974c to 97c. Rye—Nominal. Corn-Market</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Smithville Brass Band was in attend- ner we are going to have meat and pots- OTTAWA, July 11.â€”A young man named</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr"/>
@@ -2837,11 +2677,7 @@
         </is>
       </c>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: music. Much credit is due to Miss Coon long as they can. They are looking out | of the city, was attacked last night | LIVERPOOL, July 11, 11.30 a.m.â€”Spring wheat,</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr"/>
@@ -2876,11 +2712,7 @@
         </is>
       </c>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; double/multiple hyphen :: *...................................1 .7 _!== ---------â€”â€” 1.46â€” 'right side of the body. He made a | holders offer moderately. Corn steady; demand</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr"/>
@@ -2915,11 +2747,7 @@
         </is>
       </c>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: desperate struggle with the men and finally 1 fair. â€”â€¢â€”</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr"/>
@@ -2954,11 +2782,7 @@
         </is>
       </c>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L511: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and county and was one of the townshipâ€™s</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr"/>
@@ -2984,20 +2808,16 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>L730: suspicious token(s): DG6 (letter/digit mix) :: DG6 ï¼Œ 101</t>
+          <t>L730: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): DG6 (letter/digit mix) :: DG6 ， 101</t>
         </is>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 14c (letter/digit mix), 21c (letter/digit mix), 3c (letter/digit mix), 98c (letter/digit mix) :: have been bankrupt. The solutions came | 14c to 21c. Cheeseâ€”Market firm, at 3c to 98c.</t>
+          <t>L598: suspicious token(s): 14c (letter/digit mix), 21c (letter/digit mix), 3c (letter/digit mix), 98c (letter/digit mix) :: have been bankrupt. The solutions came | 14c to 21c. Cheese—Market firm, at 3c to 98c.</t>
         </is>
       </c>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing one that he especially regretted losingâ€” many very handsome presents. The TIMES</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr"/>
@@ -3032,11 +2852,7 @@
         </is>
       </c>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: Boysâ€™ Own Mission Band of Erskine Church, ---------- ____________-</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr"/>
@@ -3071,11 +2887,7 @@
         </is>
       </c>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L578: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------â€¢ | of course, they were turned out by the</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr"/>
@@ -3110,11 +2922,7 @@
         </is>
       </c>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: his way home. One of the bullets glanced | NEW YORK, July 11, 1 p. m.â€”Cottonâ€”Steady</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr"/>
@@ -3145,15 +2953,11 @@
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------â€¢ -------;â€” | for September, 862c for December. Cornâ€”494c</t>
+          <t>L607: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------• -------;— | for September, 862c for December. Corn—494c</t>
         </is>
       </c>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: - ----------â€¢ -----------Sales, 424,000 bushels No. 2 red for August</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr"/>
@@ -3188,11 +2992,7 @@
         </is>
       </c>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L591: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 974c (letter/digit mix), 97c (letter/digit mix) :: Grimsby Camp Ground Company, offered at 974c to 97c. Ryeâ€”Nominal. Corn-Market</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr"/>
@@ -3227,11 +3027,7 @@
         </is>
       </c>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 14c (letter/digit mix), 21c (letter/digit mix), 3c (letter/digit mix), 98c (letter/digit mix) :: have been bankrupt. The solutions came | 14c to 21c. Cheeseâ€”Market firm, at 3c to 98c.</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr"/>
@@ -3262,15 +3058,11 @@
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 834c (letter/digit mix) :: the officers of the Governor-Generalâ€™s Foot | September, 834c asked for December. Cornâ€”</t>
+          <t>L615: suspicious token(s): 834c (letter/digit mix) :: the officers of the Governor-General’s Foot | September, 834c asked for December. Corn—</t>
         </is>
       </c>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): 862c (letter/digit mix), 494c (letter/digit mix) :: -----------â€¢ -------;â€” | for September, 862c for December. Cornâ€”494c</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr"/>
@@ -3305,11 +3097,7 @@
         </is>
       </c>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 834c (letter/digit mix) :: the officers of the Governor-Generalâ€™s Foot | September, 834c asked for December. Cornâ€”</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr"/>
@@ -3344,11 +3132,7 @@
         </is>
       </c>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: -â€” ----------------â€¢-------------nominally for August, $7 574 for September.</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr"/>
@@ -3383,11 +3167,7 @@
         </is>
       </c>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: patrickâ€™s farm, a man by the name of Wm.</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr"/>
@@ -3422,11 +3202,7 @@
         </is>
       </c>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L693: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: arrest for being a bigamist 22 times over, | 12 oâ€™clock. Mayor Doran will handle the</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr"/>
@@ -3461,11 +3237,7 @@
         </is>
       </c>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L711: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: besides, he, owned a big farm in the in- ------- ----â€” ------------</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr"/>
@@ -3500,11 +3272,7 @@
         </is>
       </c>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L727: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Samples of New Ontario Grain. | Total salesâ€”300 tierces of lard at $8 074.</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr"/>
@@ -3539,11 +3307,7 @@
         </is>
       </c>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L731: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: day showed on â€˜Change a couple of very | UNION STOCK YARDS.-ORICAGO, July 11, 7.30</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr"/>
@@ -3578,11 +3342,7 @@
         </is>
       </c>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L737: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: in a few days.â€”Toronto Globe. ing grades, $5 50 to $5 65. Cattle-Receipts,</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr"/>
@@ -3617,11 +3377,7 @@
         </is>
       </c>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L739: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------â€¢------------I 11,000. Market fairly active.</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr"/>
@@ -3656,11 +3412,7 @@
         </is>
       </c>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L741: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: It is expected that in future the Scottish | â€”.â€”</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr"/>
@@ -3695,11 +3447,7 @@
         </is>
       </c>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L755: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”TheC anada Screw Company, of Ham- | during past week. Shipped from here to United</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr"/>
@@ -3730,11 +3478,7 @@
       </c>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L769: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜* honeymoon," however, he invariably set |sey Settlement, Ancaster, with their con-</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr"/>
@@ -3765,11 +3509,7 @@
       </c>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L793: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: children and their childrenâ€™s children and</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr"/>
@@ -3800,11 +3540,7 @@
       </c>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L794: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to the stranger, let us sayâ€”" Peace to their</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr"/>
@@ -3835,11 +3571,7 @@
       </c>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L801: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”userme</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr"/>
@@ -3870,11 +3602,7 @@
       </c>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: , â€”Mr. James Forbes, of Oneida Town-</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr"/>
@@ -3905,11 +3633,7 @@
       </c>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”While Mr. Switzer, an old man, was</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr"/>
@@ -3940,11 +3664,7 @@
       </c>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L821: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: James Cowellâ€™s drilling machine in Sen-</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr"/>
@@ -3975,11 +3695,7 @@
       </c>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Mr. H. H. Dewart, President of the</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr"/>
@@ -4010,11 +3726,7 @@
       </c>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Young Liberals' demonstration.â€”Toronto</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr"/>
@@ -4045,11 +3757,7 @@
       </c>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”The Police Magistrate yesterday gave</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr"/>
@@ -4080,11 +3788,7 @@
       </c>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Mr. William Ryckman, a farmer re-</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr"/>
@@ -4234,7 +3938,7 @@
       <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>L1107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): OHiOAGO (odd internal casing), JULy (odd internal casing) :: UNION Brock YABDS.â€” OHiOAGO, JULy 11., 7.30</t>
+          <t>L1107: suspicious token(s): OHiOAGO (odd internal casing), JULy (odd internal casing) :: UNION Brock YABDS.— OHiOAGO, JULy 11., 7.30</t>
         </is>
       </c>
       <c r="I83" s="1" t="inlineStr"/>
